--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,6 +61,12 @@
     <t>2026-05-03</t>
   </si>
   <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>1165 София К. Величков</t>
+  </si>
+  <si>
     <t>CB5768MA</t>
   </si>
   <si>
@@ -67,7 +76,19 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>10:23</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>15:39:00</t>
+  </si>
+  <si>
+    <t>3231367442 3231367442</t>
+  </si>
+  <si>
+    <t>3232342816 3232342816</t>
   </si>
   <si>
     <t>Общи литри по продукт / АНИВА ЕООД</t>
@@ -491,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,16 +521,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,119 +571,169 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1165</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>26.31</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>37.62</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>39.99</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>25.48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>1.5</v>
+      </c>
+      <c r="I3" s="1">
+        <v>38.22</v>
+      </c>
+      <c r="J3">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>40</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>103058</v>
+      <c r="N3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B8" s="6">
+        <v>51.79</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.4644</v>
+      </c>
+      <c r="E8" s="6">
+        <v>75.84</v>
+      </c>
+      <c r="F8" s="6">
+        <v>79.98999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>26.31</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.4299</v>
-      </c>
-      <c r="E7" s="6">
-        <v>37.62</v>
-      </c>
-      <c r="F7" s="6">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>26.31</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>37.62</v>
-      </c>
-      <c r="F8" s="9">
-        <v>39.99</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9">
+        <v>51.79</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>75.84</v>
+      </c>
+      <c r="F9" s="9">
+        <v>79.98999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -142,7 +142,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,12 +152,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -207,17 +201,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,22 +46,13 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-24</t>
-  </si>
-  <si>
-    <t>1165 София К. Величков</t>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>София К. Величков</t>
   </si>
   <si>
     <t>CB5768MA</t>
@@ -74,21 +62,6 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:23:00</t>
-  </si>
-  <si>
-    <t>15:39:00</t>
-  </si>
-  <si>
-    <t>3231367442 3231367442</t>
-  </si>
-  <si>
-    <t>3232342816 3232342816</t>
   </si>
   <si>
     <t>Общи литри по продукт / АНИВА ЕООД</t>
@@ -506,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -515,17 +488,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,175 +529,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2">
+        <v>25.64</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>38.97</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>40</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>26.31</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.43</v>
-      </c>
-      <c r="I2" s="1">
-        <v>37.62</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
-        <v>39.99</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6">
+        <v>25.64</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.5199</v>
+      </c>
+      <c r="E7" s="6">
+        <v>38.97</v>
+      </c>
+      <c r="F7" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>25.48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>1.5</v>
-      </c>
-      <c r="I3" s="1">
-        <v>38.22</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="B8" s="9">
+        <v>25.64</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9">
+        <v>38.97</v>
+      </c>
+      <c r="F8" s="9">
         <v>40</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="6">
-        <v>51.79</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.4644</v>
-      </c>
-      <c r="E8" s="6">
-        <v>75.84</v>
-      </c>
-      <c r="F8" s="6">
-        <v>79.98999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="9">
-        <v>51.79</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>75.84</v>
-      </c>
-      <c r="F9" s="9">
-        <v>79.98999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-06</t>
   </si>
   <si>
@@ -58,13 +67,13 @@
     <t>2026-06-21</t>
   </si>
   <si>
-    <t>София К. Величков</t>
-  </si>
-  <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>1165 София К. Величков</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>CB5768MA</t>
@@ -85,13 +94,25 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-06 10:53:38</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:24:53</t>
-  </si>
-  <si>
-    <t>2026-06-21 15:12:24</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>15:22:00</t>
+  </si>
+  <si>
+    <t>15:12:00</t>
+  </si>
+  <si>
+    <t>3232958386 3232958386</t>
+  </si>
+  <si>
+    <t>3233580327 3233580327</t>
+  </si>
+  <si>
+    <t>3233678447 3233678447</t>
   </si>
   <si>
     <t>Общи литри по продукт / АНИВА ЕООД</t>
@@ -509,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,14 +539,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,115 +583,151 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>25.64</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
         <v>1.5</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>38.46</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>40</v>
       </c>
-      <c r="K2" t="s">
-        <v>23</v>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>25.97</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>37.92</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.54</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>39.99</v>
       </c>
-      <c r="K3" t="s">
-        <v>24</v>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>26.63</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4">
         <v>1.5</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>39.94</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>41.01</v>
       </c>
-      <c r="K4" t="s">
-        <v>25</v>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:14">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -675,29 +735,29 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6">
         <v>51.61</v>
@@ -715,9 +775,9 @@
         <v>79.98999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6">
         <v>26.63</v>
@@ -735,9 +795,9 @@
         <v>41.01</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B11" s="9">
         <v>78.23999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,10 +55,16 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
-    <t>София К. Величков</t>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>1165 София К. Величков</t>
   </si>
   <si>
     <t>CB5768MA</t>
@@ -67,7 +76,19 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-03 18:20:56</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:20:00</t>
+  </si>
+  <si>
+    <t>00:18:00</t>
+  </si>
+  <si>
+    <t>3234269110 3234269110</t>
+  </si>
+  <si>
+    <t>3235049072 3235049072</t>
   </si>
   <si>
     <t>Общи литри по продукт / АНИВА ЕООД</t>
@@ -485,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -494,15 +515,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,116 +562,172 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>26.85</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
         <v>1.39</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>37.32</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.49</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>40.01</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>32.89</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>1.41</v>
+      </c>
+      <c r="I3" s="1">
+        <v>46.37</v>
+      </c>
+      <c r="J3">
+        <v>1.52</v>
+      </c>
+      <c r="K3" s="1">
+        <v>49.99</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B8" s="6">
+        <v>59.74</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.4009</v>
+      </c>
+      <c r="E8" s="6">
+        <v>83.69</v>
+      </c>
+      <c r="F8" s="6">
+        <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>26.85</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.3899</v>
-      </c>
-      <c r="E7" s="6">
-        <v>37.32</v>
-      </c>
-      <c r="F7" s="6">
-        <v>40.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>26.85</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>37.32</v>
-      </c>
-      <c r="F8" s="9">
-        <v>40.01</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9">
+        <v>59.74</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>83.69</v>
+      </c>
+      <c r="F9" s="9">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -115,7 +115,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.4009</v>
+        <v>1.400904</v>
       </c>
       <c r="E8" s="6">
         <v>83.69</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -506,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -519,13 +522,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -568,98 +571,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>26.846</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.359</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J2">
+        <v>37.289094</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L2" s="1">
+        <v>40.00054</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>26.85</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.39</v>
-      </c>
-      <c r="I2" s="1">
-        <v>37.32</v>
-      </c>
-      <c r="J2">
-        <v>1.49</v>
-      </c>
-      <c r="K2" s="1">
-        <v>40.01</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="F3">
+        <v>32.888</v>
+      </c>
+      <c r="G3" t="s">
         <v>21</v>
       </c>
-      <c r="M2">
+      <c r="H3">
+        <v>1.379</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.409</v>
+      </c>
+      <c r="J3">
+        <v>46.339192</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L3" s="1">
+        <v>49.98976</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
+      <c r="O3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>32.89</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>1.41</v>
-      </c>
-      <c r="I3" s="1">
-        <v>46.37</v>
-      </c>
-      <c r="J3">
-        <v>1.52</v>
-      </c>
-      <c r="K3" s="1">
-        <v>49.99</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -667,62 +679,62 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6">
-        <v>59.74</v>
+        <v>59.734</v>
       </c>
       <c r="C8" s="6">
         <v>2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.400904</v>
+        <v>1.400011</v>
       </c>
       <c r="E8" s="6">
-        <v>83.69</v>
+        <v>83.63</v>
       </c>
       <c r="F8" s="6">
-        <v>90</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="9">
-        <v>59.74</v>
+        <v>59.734</v>
       </c>
       <c r="C9" s="9">
         <v>2</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="9">
-        <v>83.69</v>
+        <v>83.63</v>
       </c>
       <c r="F9" s="9">
-        <v>90</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АНИВА ЕООД/АНИВА ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -117,8 +114,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -211,10 +208,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -522,13 +519,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -571,107 +568,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
       <c r="F2">
         <v>26.846</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>1.389</v>
+      </c>
+      <c r="I2" s="1">
+        <v>37.289</v>
+      </c>
+      <c r="J2">
+        <v>1.49</v>
+      </c>
+      <c r="K2" s="1">
+        <v>40.001</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.389</v>
-      </c>
-      <c r="J2">
-        <v>37.289094</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L2" s="1">
-        <v>40.00054</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>24</v>
+      <c r="N2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3">
         <v>32.888</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>1.379</v>
+        <v>1.409</v>
       </c>
       <c r="I3" s="1">
-        <v>1.409</v>
+        <v>46.339</v>
       </c>
       <c r="J3">
-        <v>46.339192</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>49.98976</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3">
+        <v>49.99</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -679,49 +667,49 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6">
         <v>59.734</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" s="7">
-        <v>1.400011</v>
-      </c>
-      <c r="E8" s="6">
-        <v>83.63</v>
-      </c>
-      <c r="F8" s="6">
-        <v>89.98999999999999</v>
+        <v>1.4</v>
+      </c>
+      <c r="E8" s="7">
+        <v>83.628</v>
+      </c>
+      <c r="F8" s="7">
+        <v>89.991</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="9">
         <v>59.734</v>
@@ -731,10 +719,10 @@
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="9">
-        <v>83.63</v>
+        <v>83.628</v>
       </c>
       <c r="F9" s="9">
-        <v>89.98999999999999</v>
+        <v>89.991</v>
       </c>
     </row>
   </sheetData>
